--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
@@ -1654,7 +1654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>**見える化システムでは研修系の指標（J1〜J15）が本町では未公表。**計画素案 施策6の成果指標の現状値。**初期集中支援チームの訪問実績が0件である理由も併せて確認したい**</t>
+          <t>**見える化システムでは研修系の指標（J1〜J15）が本町では未公表。**計画素案 施策6の成果指標の現状値。**見える化の直近値は初期集中支援チームが令和5年度、推進員が令和6年3月、カフェが令和6年4月であり、令和6・7年度の実績が要る。**訪問実績0件は県内59市町村のうち30団体に共通しており（中央値0件）、本町だけの状況ではない。**件数そのものより、対象者の把握経路（医療機関・地域包括支援センター・民生委員からの連絡）が機能しているかを確認したい。**あわせて推進員4人の職種・配置先・活動内容もご教示いただきたい</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr"/>
@@ -2105,42 +2105,42 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>H9-2</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>最優先</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>防災担当</t>
+          <t>介護保険担当</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>避難行動要支援者名簿と個別避難計画の状況</t>
+          <t>認知症高齢者自立度Ⅲa・Ⅲbの人数</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>①名簿の登載者数（うち要介護認定者・障がい者手帳所持者）②平常時からの情報提供に同意している人数 ③個別避難計画の策定件数 ④福祉避難所の指定数と受入可能人数</t>
+          <t>認知症高齢者の日常生活自立度別の認定者数（自立・Ⅰ・Ⅱa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・M）</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>令和8年4月1日現在</t>
+          <t>令和6年度・令和7年度</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>人／件／か所</t>
+          <t>人</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>計画素案 施策7の成果指標の現状値。**調査から一人で避難できない方は約495人と推計され、分母（対象者の定義）を決めないと策定率が意味を持たない**</t>
+          <t>**受領資料にはⅡa・Ⅱb・Ⅳ・Mしかなく、計画に載せる「自立度Ⅱ以上」の合計が出せない。**見える化システムのＢ7（認知症高齢者自立度の状況）の出力でも可。認知症基本法第13条第1項は「当該市町村の実情に即した」計画を求めており、仕様書4(1)①イも統計分析の対象に認知症高齢者数を挙げている</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H9-3</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -2158,32 +2158,32 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>福祉担当</t>
+          <t>介護保険担当</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>高齢者福祉サービスの利用実績</t>
+          <t>認知症総合支援事業費の額</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>①移送・外出支援 ②配食サービス ③緊急通報装置 ④介護用品給付券 ⑤その他の町単独事業　の利用者数・実施件数・事業費</t>
+          <t>包括的支援事業・任意事業費のうち、認知症初期集中支援推進事業と認知症地域支援・ケア向上事業の決算額</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>令和5〜7年度</t>
+          <t>令和3〜7年度</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>人／件／千円</t>
+          <t>円</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>計画素案 施策8の成果指標の現状値。**介護用品給付券等の町単独事業は、財源科目と地域支援事業の補助対象の可否を併せて確認したい**</t>
+          <t>**年報 様式4 では包括的支援事業・任意事業が一括（令和6年度29,335千円）で、事業別の内訳がない。**本町の認知症施策の規模を示す唯一の金額であり、第10期に施策を拡充したときにどれだけ動くかが見えない</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H9-4</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -2206,27 +2206,27 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>短期入所の利用状況</t>
+          <t>町内の若年性認知症の方の把握状況</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>利用者数・利用日数（予防を含む）。緊急利用の件数</t>
+          <t>65歳未満で認知症の診断を受けている方の人数、就労・相談の状況</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>令和5〜7年度</t>
+          <t>令和7年度</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>人／日</t>
+          <t>人</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>**レスパイトを第10期の重点とするため。**在宅の認定者の未利用理由の16.9％が「家族が介護している」</t>
+          <t>**認知症基本法第16条第2項は若年性認知症の人の雇用の継続・円滑な就職に資する施策を求めている。**第2号被保険者の認定者は令和8年3月末で9人。該当がない場合もその旨を計画に書く</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr"/>
@@ -2234,42 +2234,42 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>H13</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>介護保険担当</t>
+          <t>防災担当</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>介護給付適正化事業の実施状況</t>
+          <t>避難行動要支援者名簿と個別避難計画の状況</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>①要介護認定の適正化 ②ケアプラン点検 ③医療情報との突合・縦覧点検 ④住宅改修等の点検 ⑤福祉用具貸与調査　の実施件数</t>
+          <t>①名簿の登載者数（うち要介護認定者・障がい者手帳所持者）②平常時からの情報提供に同意している人数 ③個別避難計画の策定件数 ④福祉避難所の指定数と受入可能人数</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>令和5〜7年度</t>
+          <t>令和8年4月1日現在</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>人／件／か所</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>計画素案 施策10の成果指標の現状値</t>
+          <t>計画素案 施策7の成果指標の現状値。**調査から一人で避難できない方は約495人と推計され、分母（対象者の定義）を決めないと策定率が意味を持たない**</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr"/>
@@ -2277,27 +2277,27 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>H14</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>介護保険担当</t>
+          <t>福祉担当</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>要介護度の維持・改善の状況</t>
+          <t>高齢者福祉サービスの利用実績</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>更新認定における前回との比較（改善・維持・悪化の別）</t>
+          <t>①移送・外出支援 ②配食サービス ③緊急通報装置 ④介護用品給付券 ⑤その他の町単独事業　の利用者数・実施件数・事業費</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>人／件／千円</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>計画素案 施策10の成果指標の現状値。**認定者800人規模では数人の変動で率が動くため、3年分が必要**</t>
+          <t>計画素案 施策8の成果指標の現状値。**介護用品給付券等の町単独事業は、財源科目と地域支援事業の補助対象の可否を併せて確認したい**</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -2335,27 +2335,27 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>事業所別の定員・稼働率・町内外利用</t>
+          <t>短期入所の利用状況</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>施設・居住系サービスの事業所別定員、稼働率、待機者数、休廃止の予定。町内の方の町外事業所利用の状況</t>
+          <t>利用者数・利用日数（予防を含む）。緊急利用の件数</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>令和8年4月1日現在</t>
+          <t>令和5〜7年度</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>人／％</t>
+          <t>人／日</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>供給制約の確認。**認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ27人（38.0％）増えている経緯も併せて確認したい**（第9期は「新規施設整備は原則行わない」方針）</t>
+          <t>**レスパイトを第10期の重点とするため。**在宅の認定者の未利用理由の16.9％が「家族が介護している」</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr"/>
@@ -2363,12 +2363,12 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>H16</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>令和7年度調査の個票データ</t>
+          <t>介護給付適正化事業の実施状況</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>介護予防・日常生活圏域ニーズ調査、在宅介護実態調査の個票（CSV等）。**地区情報の有無も併せて確認したい**</t>
+          <t>①要介護認定の適正化 ②ケアプラン点検 ③医療情報との突合・縦覧点検 ④住宅改修等の点検 ⑤福祉用具貸与調査　の実施件数</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>令和7年度</t>
+          <t>令和5〜7年度</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>**要介護度別・世帯構成別のクロス集計17件に必要。**報告書の単純集計では、認定状況別・年齢別・男女別までしか分解できない</t>
+          <t>計画素案 施策10の成果指標の現状値</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr"/>
@@ -2406,45 +2406,174 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>要介護度の維持・改善の状況</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>更新認定における前回との比較（改善・維持・悪化の別）</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>令和5〜7年度</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>計画素案 施策10の成果指標の現状値。**認定者800人規模では数人の変動で率が動くため、3年分が必要**</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>事業所別の定員・稼働率・町内外利用</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>施設・居住系サービスの事業所別定員、稼働率、待機者数、休廃止の予定。町内の方の町外事業所利用の状況</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>令和8年4月1日現在</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>人／％</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>供給制約の確認。**認知症対応型共同生活介護の定員が令和4年度71人から令和6年度98人へ27人（38.0％）増えている経緯も併せて確認したい**（第9期は「新規施設整備は原則行わない」方針）。**介護保険法第117条第2項第1号が求める必要利用定員総数の設定に直結する。**町内定員98人に対し本町の被保険者の利用は月45人台であり、町外の方の利用割合をご教示いただきたい</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>令和7年度調査の個票データ</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活圏域ニーズ調査、在宅介護実態調査の個票（CSV等）。**地区情報の有無も併せて確認したい**</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>**要介護度別・世帯構成別のクロス集計17件に必要。**報告書の単純集計では、認定状況別・年齢別・男女別までしか分解できない</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>H17</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>介護保険担当</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>令和7年度調査の調査票・配布数・回収数・実施時期</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>調査票の現物、配布数、回収数、回収率、実施時期。**在宅介護実態調査の配布方法（ケアマネジャー経由か否か）**</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>**在宅介護実態調査がケアマネジャー経由の配布であった場合、サービス未利用者が構造的に対象外となり、認定と利用のギャップを検証できない。**補足調査の要否の判断に直結する。また、報告書内で回収数319件と集計n=366件が一致しない箇所がある</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2830,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3100,22 +3229,22 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C8-2</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>保険料算定のケース設定</t>
+          <t>認知症の人及びその家族等の意見の聴き方</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>仕様書4(2)は「新たに介護施設を整備する場合や制度改正により条件が変わる場合等、想定されるケースごとに保険料の算定を行う」と定める</t>
+          <t>**共生社会の実現を推進するための認知症基本法第13条第3項が準用する第12条第3項は、市町村認知症施策推進計画の案の作成にあたり認知症の人及びその家族等の意見を聴くよう努めることを定めている。**記述の追加では埋まらず、策定過程そのものに関わる</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>①計画期間中に施設・居住系サービスを整備する予定があるか ②基金の取崩方針（据置・引下げ・積立）についての町の考え</t>
+          <t>①小野町高齢者福祉サービス推進協議会の委員に認知症の人又はその家族が含まれるか ②含まれない場合、家族会・認知症カフェ等で意見を聴く機会を設けるか ③意見を聴いた経過を計画の策定経過に記載してよいか</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3128,27 +3257,27 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C8-3</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>工程の変更</t>
+          <t>福島県の認知症施策推進計画の策定状況</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>障がい計画は仕様書7の工程（調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅れている。**仕様書11④は基本事項の変更を双方協議で定めるとし、仕様書8①は受託者が打合せ記録を作成し相互に確認すると定める**</t>
+          <t>認知症基本法第13条第1項は、都道府県計画が策定されているときは国の基本計画と都道府県計画の両方を基本とすることを求めている</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>変更後の工程について協議し、打合せ記録として相互確認したい。変更工程表の案は別途提出する</t>
+          <t>福島県の認知症施策推進計画が策定されているか。策定済みの場合、その内容と本町の計画との関係</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>8月19日の協議会又はその前後</t>
+          <t>10月中</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr"/>
@@ -3156,27 +3285,27 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>電子回答（QRコード）の併用</t>
+          <t>保険料算定のケース設定</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>障がい者ニーズ調査の回収率66.7％の達成手段の一つ。仕様書に定めがない</t>
+          <t>仕様書4(2)は「新たに介護施設を整備する場合や制度改正により条件が変わる場合等、想定されるケースごとに保険料の算定を行う」と定める</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>電子回答を併用してよいか。可の場合、個人情報の取扱いをどう整理するか</t>
+          <t>①計画期間中に施設・居住系サービスを整備する予定があるか ②基金の取崩方針（据置・引下げ・積立）についての町の考え</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>8月中</t>
+          <t>9月中</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr"/>
@@ -3184,30 +3313,86 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>工程の変更</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>障がい計画は仕様書7の工程（調査は7月まで、骨子案9月、骨子案検討10月）から3〜4か月遅れている。**仕様書11④は基本事項の変更を双方協議で定めるとし、仕様書8①は受託者が打合せ記録を作成し相互に確認すると定める**</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>変更後の工程について協議し、打合せ記録として相互確認したい。変更工程表の案は別途提出する</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>8月19日の協議会又はその前後</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>電子回答（QRコード）の併用</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>障がい者ニーズ調査の回収率66.7％の達成手段の一つ。仕様書に定めがない</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>電子回答を併用してよいか。可の場合、個人情報の取扱いをどう整理するか</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>8月中</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>調査の地域別集計の粒度</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>仕様書5(1)は地域別のクロス集計を明示要件とする。**行政区単位では1セルあたりの回答数が1桁になり、公表できない**</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>地域区分を小学校区又はこれに準じる粒度としてよいか</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>調査票の確定前</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3314,16 +3499,16 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>0</v>
@@ -3358,16 +3543,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>
@@ -3380,7 +3565,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="13" t="inlineStr"/>
       <c r="D7" s="13" t="inlineStr"/>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
@@ -1281,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1642,6 +1642,49 @@
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>**保険者機能強化推進交付金等の評価指標（市町村分）と小野町の得点票**</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>①評価指標（市町村分）の本体　②小野町の該当状況調査票・得点票（令和6・7・8年度の3か年）　③全国一覧表</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>令和6〜8年度</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>**令和8年9月25日に受領した公表資料は都道府県分のみで、小野町自身の得点分析ができていない。**市町村分がそろえば、全国の多くが得点していて小野町が0点の項目を洗い出し、**新たな事業も予算も要さず計画への記載だけで取れるものを切り分けられる**（（ⅰ）体制・取組の指標は計画の書きぶりで動くため）。評価結果を外部の議論の場で検証することは評価指標自体の要件でもあり、毎年度の協議会資料として整理する</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3239,7 +3282,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>**共生社会の実現を推進するための認知症基本法第13条第3項が準用する第12条第3項は、市町村認知症施策推進計画の案の作成にあたり認知症の人及びその家族等の意見を聴くよう努めることを定めている。**記述の追加では埋まらず、策定過程そのものに関わる</t>
+          <t>**共生社会の実現を推進するための認知症基本法第13条第3項が準用する第12条第3項は、市町村認知症施策推進計画の案の作成にあたり認知症の人及びその家族等の意見を聴くよう努めることを定めている。**記述の追加では埋まらず、策定過程そのものに関わる。**あわせて、介護保険保険者努力支援交付金の市町村分の評価指標に「認知症の人及びその家族等の意見を踏まえた市町村認知症施策推進計画の策定に着手している」という項目があるとされる（配点5点）。努力義務であると同時に交付金の得点の条件でもある可能性があり、市町村分の評価指標の受領後に確認する**</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3477,13 +3520,13 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -3543,13 +3586,13 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>8</v>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
@@ -1281,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1685,6 +1685,92 @@
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>**厚生労働省の保険者別配布シート（将来推計の精度検証）**</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>国が全国の保険者に標準の推計方法を当てはめ、推計値÷実績値を算定したもの。**基本推計（性別・年齢5歳階級別・要介護度別）と包括推計の別**、全国順位・県内順位を含む</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>令和6・7年度</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>**推計手法の選択が小野町にとって正しいかを、国のデータで確かめられる。**見える化システムの将来推計は手法を選ばせるが、どちらが当たるかは保険者ごとに違う。他町村の案件では、このシートにより基本推計が包括推計を大きく上回ることを確認して手法を確定している</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>介護保険担当</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>**第9期策定時の見える化システムの設定**</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>①基準年度　②認定率の伸びの窓　③利用率の伸びの窓　④推計手法（基本推計／包括推計）</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>**第9期の見込みは3か年の振れ幅が0.42％で自然体推計そのものであり、その水準は令和5年度の実績より7.3％高い。**実績／見込みが令和6年度98.6％・令和7年度91.1％となった原因を確定できる。第10期で同じ置き方を繰り返さないために要する</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3520,16 +3606,16 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>0</v>
@@ -3586,16 +3672,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_データ依頼票_20260813.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>保険料算定に必須。**繰越金182.0百万円・基金純増88.1百万円という財政余剰の扱いが第10期の保険料水準を左右する**</t>
+          <t>保険料算定に必須。**繰越金182.0百万円・基金残高120.0百万円（令和5年度末）という財政余剰の扱いが第10期の保険料水準を左右する**</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr"/>
